--- a/public/templates/SDC Risk Register Template.xlsx
+++ b/public/templates/SDC Risk Register Template.xlsx
@@ -165,21 +165,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 High</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Likely</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Months</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="G2">
-        <f>IFERROR(MATCH(E2,Lists!$C$2:$C$6,0)*MATCH(F2,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E2,Lists!$C$2:$C$4,0)*MATCH(F2,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H2"/>
       <c r="I2" t="inlineStr">
@@ -209,21 +209,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4 High</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Likely</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weeks</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="G3">
-        <f>IFERROR(MATCH(E3,Lists!$C$2:$C$6,0)*MATCH(F3,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E3,Lists!$C$2:$C$4,0)*MATCH(F3,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H3"/>
       <c r="I3" t="inlineStr">
@@ -253,21 +253,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Low</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="G4">
-        <f>IFERROR(MATCH(E4,Lists!$C$2:$C$6,0)*MATCH(F4,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E4,Lists!$C$2:$C$4,0)*MATCH(F4,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H4"/>
       <c r="I4" t="inlineStr">
@@ -291,7 +291,7 @@
       <c r="E5"/>
       <c r="F5"/>
       <c r="G5">
-        <f>IFERROR(MATCH(E5,Lists!$C$2:$C$6,0)*MATCH(F5,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E5,Lists!$C$2:$C$4,0)*MATCH(F5,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -307,7 +307,7 @@
       <c r="E6"/>
       <c r="F6"/>
       <c r="G6">
-        <f>IFERROR(MATCH(E6,Lists!$C$2:$C$6,0)*MATCH(F6,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E6,Lists!$C$2:$C$4,0)*MATCH(F6,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -323,7 +323,7 @@
       <c r="E7"/>
       <c r="F7"/>
       <c r="G7">
-        <f>IFERROR(MATCH(E7,Lists!$C$2:$C$6,0)*MATCH(F7,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E7,Lists!$C$2:$C$4,0)*MATCH(F7,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -339,7 +339,7 @@
       <c r="E8"/>
       <c r="F8"/>
       <c r="G8">
-        <f>IFERROR(MATCH(E8,Lists!$C$2:$C$6,0)*MATCH(F8,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E8,Lists!$C$2:$C$4,0)*MATCH(F8,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H8"/>
       <c r="I8"/>
@@ -355,7 +355,7 @@
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9">
-        <f>IFERROR(MATCH(E9,Lists!$C$2:$C$6,0)*MATCH(F9,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E9,Lists!$C$2:$C$4,0)*MATCH(F9,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H9"/>
       <c r="I9"/>
@@ -371,7 +371,7 @@
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10">
-        <f>IFERROR(MATCH(E10,Lists!$C$2:$C$6,0)*MATCH(F10,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E10,Lists!$C$2:$C$4,0)*MATCH(F10,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H10"/>
       <c r="I10"/>
@@ -387,7 +387,7 @@
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11">
-        <f>IFERROR(MATCH(E11,Lists!$C$2:$C$6,0)*MATCH(F11,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E11,Lists!$C$2:$C$4,0)*MATCH(F11,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -403,7 +403,7 @@
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12">
-        <f>IFERROR(MATCH(E12,Lists!$C$2:$C$6,0)*MATCH(F12,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E12,Lists!$C$2:$C$4,0)*MATCH(F12,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H12"/>
       <c r="I12"/>
@@ -419,7 +419,7 @@
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13">
-        <f>IFERROR(MATCH(E13,Lists!$C$2:$C$6,0)*MATCH(F13,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E13,Lists!$C$2:$C$4,0)*MATCH(F13,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H13"/>
       <c r="I13"/>
@@ -435,7 +435,7 @@
       <c r="E14"/>
       <c r="F14"/>
       <c r="G14">
-        <f>IFERROR(MATCH(E14,Lists!$C$2:$C$6,0)*MATCH(F14,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E14,Lists!$C$2:$C$4,0)*MATCH(F14,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H14"/>
       <c r="I14"/>
@@ -451,7 +451,7 @@
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15">
-        <f>IFERROR(MATCH(E15,Lists!$C$2:$C$6,0)*MATCH(F15,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E15,Lists!$C$2:$C$4,0)*MATCH(F15,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H15"/>
       <c r="I15"/>
@@ -467,7 +467,7 @@
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16">
-        <f>IFERROR(MATCH(E16,Lists!$C$2:$C$6,0)*MATCH(F16,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E16,Lists!$C$2:$C$4,0)*MATCH(F16,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H16"/>
       <c r="I16"/>
@@ -483,7 +483,7 @@
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17">
-        <f>IFERROR(MATCH(E17,Lists!$C$2:$C$6,0)*MATCH(F17,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E17,Lists!$C$2:$C$4,0)*MATCH(F17,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H17"/>
       <c r="I17"/>
@@ -499,7 +499,7 @@
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18">
-        <f>IFERROR(MATCH(E18,Lists!$C$2:$C$6,0)*MATCH(F18,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E18,Lists!$C$2:$C$4,0)*MATCH(F18,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H18"/>
       <c r="I18"/>
@@ -515,7 +515,7 @@
       <c r="E19"/>
       <c r="F19"/>
       <c r="G19">
-        <f>IFERROR(MATCH(E19,Lists!$C$2:$C$6,0)*MATCH(F19,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E19,Lists!$C$2:$C$4,0)*MATCH(F19,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H19"/>
       <c r="I19"/>
@@ -531,7 +531,7 @@
       <c r="E20"/>
       <c r="F20"/>
       <c r="G20">
-        <f>IFERROR(MATCH(E20,Lists!$C$2:$C$6,0)*MATCH(F20,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E20,Lists!$C$2:$C$4,0)*MATCH(F20,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H20"/>
       <c r="I20"/>
@@ -547,7 +547,7 @@
       <c r="E21"/>
       <c r="F21"/>
       <c r="G21">
-        <f>IFERROR(MATCH(E21,Lists!$C$2:$C$6,0)*MATCH(F21,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E21,Lists!$C$2:$C$4,0)*MATCH(F21,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H21"/>
       <c r="I21"/>
@@ -563,7 +563,7 @@
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22">
-        <f>IFERROR(MATCH(E22,Lists!$C$2:$C$6,0)*MATCH(F22,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E22,Lists!$C$2:$C$4,0)*MATCH(F22,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H22"/>
       <c r="I22"/>
@@ -579,7 +579,7 @@
       <c r="E23"/>
       <c r="F23"/>
       <c r="G23">
-        <f>IFERROR(MATCH(E23,Lists!$C$2:$C$6,0)*MATCH(F23,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E23,Lists!$C$2:$C$4,0)*MATCH(F23,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H23"/>
       <c r="I23"/>
@@ -595,7 +595,7 @@
       <c r="E24"/>
       <c r="F24"/>
       <c r="G24">
-        <f>IFERROR(MATCH(E24,Lists!$C$2:$C$6,0)*MATCH(F24,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E24,Lists!$C$2:$C$4,0)*MATCH(F24,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H24"/>
       <c r="I24"/>
@@ -611,7 +611,7 @@
       <c r="E25"/>
       <c r="F25"/>
       <c r="G25">
-        <f>IFERROR(MATCH(E25,Lists!$C$2:$C$6,0)*MATCH(F25,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E25,Lists!$C$2:$C$4,0)*MATCH(F25,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H25"/>
       <c r="I25"/>
@@ -627,7 +627,7 @@
       <c r="E26"/>
       <c r="F26"/>
       <c r="G26">
-        <f>IFERROR(MATCH(E26,Lists!$C$2:$C$6,0)*MATCH(F26,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E26,Lists!$C$2:$C$4,0)*MATCH(F26,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H26"/>
       <c r="I26"/>
@@ -643,7 +643,7 @@
       <c r="E27"/>
       <c r="F27"/>
       <c r="G27">
-        <f>IFERROR(MATCH(E27,Lists!$C$2:$C$6,0)*MATCH(F27,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E27,Lists!$C$2:$C$4,0)*MATCH(F27,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H27"/>
       <c r="I27"/>
@@ -659,7 +659,7 @@
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28">
-        <f>IFERROR(MATCH(E28,Lists!$C$2:$C$6,0)*MATCH(F28,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E28,Lists!$C$2:$C$4,0)*MATCH(F28,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H28"/>
       <c r="I28"/>
@@ -675,7 +675,7 @@
       <c r="E29"/>
       <c r="F29"/>
       <c r="G29">
-        <f>IFERROR(MATCH(E29,Lists!$C$2:$C$6,0)*MATCH(F29,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E29,Lists!$C$2:$C$4,0)*MATCH(F29,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H29"/>
       <c r="I29"/>
@@ -691,7 +691,7 @@
       <c r="E30"/>
       <c r="F30"/>
       <c r="G30">
-        <f>IFERROR(MATCH(E30,Lists!$C$2:$C$6,0)*MATCH(F30,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E30,Lists!$C$2:$C$4,0)*MATCH(F30,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H30"/>
       <c r="I30"/>
@@ -707,7 +707,7 @@
       <c r="E31"/>
       <c r="F31"/>
       <c r="G31">
-        <f>IFERROR(MATCH(E31,Lists!$C$2:$C$6,0)*MATCH(F31,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E31,Lists!$C$2:$C$4,0)*MATCH(F31,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H31"/>
       <c r="I31"/>
@@ -723,7 +723,7 @@
       <c r="E32"/>
       <c r="F32"/>
       <c r="G32">
-        <f>IFERROR(MATCH(E32,Lists!$C$2:$C$6,0)*MATCH(F32,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E32,Lists!$C$2:$C$4,0)*MATCH(F32,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H32"/>
       <c r="I32"/>
@@ -739,7 +739,7 @@
       <c r="E33"/>
       <c r="F33"/>
       <c r="G33">
-        <f>IFERROR(MATCH(E33,Lists!$C$2:$C$6,0)*MATCH(F33,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E33,Lists!$C$2:$C$4,0)*MATCH(F33,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H33"/>
       <c r="I33"/>
@@ -755,7 +755,7 @@
       <c r="E34"/>
       <c r="F34"/>
       <c r="G34">
-        <f>IFERROR(MATCH(E34,Lists!$C$2:$C$6,0)*MATCH(F34,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E34,Lists!$C$2:$C$4,0)*MATCH(F34,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H34"/>
       <c r="I34"/>
@@ -771,7 +771,7 @@
       <c r="E35"/>
       <c r="F35"/>
       <c r="G35">
-        <f>IFERROR(MATCH(E35,Lists!$C$2:$C$6,0)*MATCH(F35,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E35,Lists!$C$2:$C$4,0)*MATCH(F35,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H35"/>
       <c r="I35"/>
@@ -787,7 +787,7 @@
       <c r="E36"/>
       <c r="F36"/>
       <c r="G36">
-        <f>IFERROR(MATCH(E36,Lists!$C$2:$C$6,0)*MATCH(F36,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E36,Lists!$C$2:$C$4,0)*MATCH(F36,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H36"/>
       <c r="I36"/>
@@ -803,7 +803,7 @@
       <c r="E37"/>
       <c r="F37"/>
       <c r="G37">
-        <f>IFERROR(MATCH(E37,Lists!$C$2:$C$6,0)*MATCH(F37,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E37,Lists!$C$2:$C$4,0)*MATCH(F37,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H37"/>
       <c r="I37"/>
@@ -819,7 +819,7 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38">
-        <f>IFERROR(MATCH(E38,Lists!$C$2:$C$6,0)*MATCH(F38,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E38,Lists!$C$2:$C$4,0)*MATCH(F38,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H38"/>
       <c r="I38"/>
@@ -835,7 +835,7 @@
       <c r="E39"/>
       <c r="F39"/>
       <c r="G39">
-        <f>IFERROR(MATCH(E39,Lists!$C$2:$C$6,0)*MATCH(F39,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E39,Lists!$C$2:$C$4,0)*MATCH(F39,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H39"/>
       <c r="I39"/>
@@ -851,7 +851,7 @@
       <c r="E40"/>
       <c r="F40"/>
       <c r="G40">
-        <f>IFERROR(MATCH(E40,Lists!$C$2:$C$6,0)*MATCH(F40,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E40,Lists!$C$2:$C$4,0)*MATCH(F40,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H40"/>
       <c r="I40"/>
@@ -867,7 +867,7 @@
       <c r="E41"/>
       <c r="F41"/>
       <c r="G41">
-        <f>IFERROR(MATCH(E41,Lists!$C$2:$C$6,0)*MATCH(F41,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E41,Lists!$C$2:$C$4,0)*MATCH(F41,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H41"/>
       <c r="I41"/>
@@ -883,7 +883,7 @@
       <c r="E42"/>
       <c r="F42"/>
       <c r="G42">
-        <f>IFERROR(MATCH(E42,Lists!$C$2:$C$6,0)*MATCH(F42,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E42,Lists!$C$2:$C$4,0)*MATCH(F42,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H42"/>
       <c r="I42"/>
@@ -899,7 +899,7 @@
       <c r="E43"/>
       <c r="F43"/>
       <c r="G43">
-        <f>IFERROR(MATCH(E43,Lists!$C$2:$C$6,0)*MATCH(F43,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E43,Lists!$C$2:$C$4,0)*MATCH(F43,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H43"/>
       <c r="I43"/>
@@ -915,7 +915,7 @@
       <c r="E44"/>
       <c r="F44"/>
       <c r="G44">
-        <f>IFERROR(MATCH(E44,Lists!$C$2:$C$6,0)*MATCH(F44,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E44,Lists!$C$2:$C$4,0)*MATCH(F44,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H44"/>
       <c r="I44"/>
@@ -931,7 +931,7 @@
       <c r="E45"/>
       <c r="F45"/>
       <c r="G45">
-        <f>IFERROR(MATCH(E45,Lists!$C$2:$C$6,0)*MATCH(F45,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E45,Lists!$C$2:$C$4,0)*MATCH(F45,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H45"/>
       <c r="I45"/>
@@ -947,7 +947,7 @@
       <c r="E46"/>
       <c r="F46"/>
       <c r="G46">
-        <f>IFERROR(MATCH(E46,Lists!$C$2:$C$6,0)*MATCH(F46,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E46,Lists!$C$2:$C$4,0)*MATCH(F46,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H46"/>
       <c r="I46"/>
@@ -963,7 +963,7 @@
       <c r="E47"/>
       <c r="F47"/>
       <c r="G47">
-        <f>IFERROR(MATCH(E47,Lists!$C$2:$C$6,0)*MATCH(F47,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E47,Lists!$C$2:$C$4,0)*MATCH(F47,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H47"/>
       <c r="I47"/>
@@ -979,7 +979,7 @@
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48">
-        <f>IFERROR(MATCH(E48,Lists!$C$2:$C$6,0)*MATCH(F48,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E48,Lists!$C$2:$C$4,0)*MATCH(F48,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H48"/>
       <c r="I48"/>
@@ -995,7 +995,7 @@
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49">
-        <f>IFERROR(MATCH(E49,Lists!$C$2:$C$6,0)*MATCH(F49,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E49,Lists!$C$2:$C$4,0)*MATCH(F49,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H49"/>
       <c r="I49"/>
@@ -1011,7 +1011,7 @@
       <c r="E50"/>
       <c r="F50"/>
       <c r="G50">
-        <f>IFERROR(MATCH(E50,Lists!$C$2:$C$6,0)*MATCH(F50,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E50,Lists!$C$2:$C$4,0)*MATCH(F50,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H50"/>
       <c r="I50"/>
@@ -1027,7 +1027,7 @@
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51">
-        <f>IFERROR(MATCH(E51,Lists!$C$2:$C$6,0)*MATCH(F51,Lists!$D$2:$D$4,0),"")</f>
+        <f>IFERROR(MATCH(E51,Lists!$C$2:$C$4,0)*MATCH(F51,Lists!$D$2:$D$4,0),"")</f>
       </c>
       <c r="H51"/>
       <c r="I51"/>
@@ -1035,16 +1035,16 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Category must be Technical, Supply chain, Resource or Safety." sqref="C2:C51">
-      <formula1>Lists!$A$2:$A$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Category must be Technical, Supply chain, Resource, Safety or All." sqref="C2:C51">
+      <formula1>Lists!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Complexity runs 1 Low to 5 Very high." sqref="D2:D51">
-      <formula1>Lists!$B$2:$B$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Complexity is Low, Medium or High." sqref="D2:D51">
+      <formula1>Lists!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Chance runs Rare to Almost certain." sqref="E2:E51">
-      <formula1>Lists!$C$2:$C$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Chance is Low, Medium or High." sqref="E2:E51">
+      <formula1>Lists!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Impact is Days, Weeks or Months." sqref="F2:F51">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Impact is Low, Medium or High." sqref="F2:F51">
       <formula1>Lists!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Not one of the options" error="Status is Active or Resolved." sqref="J2:J51">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 Low</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rare</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 Fairly low</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unlikely</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weeks</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1156,17 +1156,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Moderate</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Possible</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Months</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="E4"/>
@@ -1177,31 +1177,19 @@
           <t xml:space="preserve">Safety</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4 High</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Likely</t>
-        </is>
-      </c>
+      <c r="B5"/>
+      <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
     </row>
     <row r="6">
-      <c r="A6"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 Very high</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Almost certain</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="B6"/>
+      <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
     </row>
